--- a/output/pdf_financials_xlsx/RIC.xlsx
+++ b/output/pdf_financials_xlsx/RIC.xlsx
@@ -2748,13 +2748,13 @@
         <v>0.006168</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.008116</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.006187</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.005929</v>
       </c>
     </row>
     <row r="35">
@@ -2846,13 +2846,13 @@
         <v>0.006168</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.008116</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.006187</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.005929</v>
       </c>
     </row>
     <row r="37">
@@ -3434,13 +3434,13 @@
         <v>0.005453</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.017124</v>
+        <v>0.009008</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.011365</v>
+        <v>0.005178</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.016051</v>
+        <v>0.010122</v>
       </c>
     </row>
     <row r="49">
@@ -7212,13 +7212,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008706999999999999</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009271</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011951</v>
       </c>
     </row>
     <row r="125">
@@ -7261,13 +7261,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008706999999999999</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009271</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0.069828</v>
+        <v>0.057877</v>
       </c>
     </row>
     <row r="126">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -34782,7 +34782,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -35684,7 +35688,11 @@
           <t>Lease payments 12,15</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -58100,7 +58108,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">

--- a/output/pdf_financials_xlsx/RIC.xlsx
+++ b/output/pdf_financials_xlsx/RIC.xlsx
@@ -39292,7 +39292,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -40814,7 +40818,11 @@
           <t>Additions to intangible assets 13 —</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RIC.xlsx
+++ b/output/pdf_financials_xlsx/RIC.xlsx
@@ -4216,43 +4216,43 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.014574</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0.018604</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.017122</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.015949</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.016359</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.018247</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.02436</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.022373</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.024563</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.03145</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.04347</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.044643</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.042335</v>
       </c>
     </row>
     <row r="65">
@@ -47708,7 +47708,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E473" s="5" t="n">
         <v>-3.932</v>
       </c>
